--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260609.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.24%</t>
+          <t>12.81%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>929,687,000</t>
+          <t>535,870,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>11.65%</t>
+          <t>12.27%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>511,060,000</t>
+          <t>919,017,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.36%</t>
+          <t>11.65%</t>
         </is>
       </c>
     </row>
@@ -677,122 +677,122 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>107,900,000</t>
+          <t>123,100,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>8.46%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>36,570,000</t>
+          <t>1,112,330,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>6.02%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1,112,330,000</t>
+          <t>35,830,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.58%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>219,032,000</t>
+          <t>104,423,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>108,683,000</t>
+          <t>41,195,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>41,195,000</t>
+          <t>146,022,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>497,600,000</t>
+          <t>590,960,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>286,174,000</t>
+          <t>16,700,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>14,050,000</t>
+          <t>279,434,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -897,100 +897,100 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>71,560,000</t>
+          <t>85,040,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>28,480,000</t>
+          <t>8,800,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7,420,000</t>
+          <t>52,700,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>72,239,000</t>
+          <t>27,970,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>44,310,000</t>
+          <t>72,239,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1012,359 +1012,359 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>18,910,000</t>
+          <t>49,040,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>86,910,000</t>
+          <t>10,514,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,014,000</t>
+          <t>156,740,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13,894,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>42,230,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,496,000</t>
+          <t>7,580,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>41,320,000</t>
+          <t>12,600,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,822,441</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>131,610,000</t>
+          <t>89,440,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>44,730,000</t>
+          <t>57,950,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>55,740,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>9,274,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>16,280,000</t>
+          <t>2,336,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>46,930,000</t>
+          <t>9,816,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>75,340,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>16,280,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1381,100 +1381,100 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>27,979,000</t>
+          <t>27,779,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,799,000</t>
+          <t>15,212,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,290,000</t>
+          <t>57,220,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,770,000</t>
+          <t>21,200,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>48,290,000</t>
+          <t>7,770,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1503,127 +1503,127 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>19,910,000</t>
+          <t>10,820,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>16,560,000</t>
+          <t>22,331,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>22,840,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,840,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>9,110,000</t>
+          <t>19,910,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>19,240,000</t>
+          <t>31,540,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,66 +1635,66 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>20,040,000</t>
+          <t>5,199,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>16,161,000</t>
+          <t>11,040,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>26,550,000</t>
+          <t>10,771,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>26,900,000</t>
+          <t>17,940,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2,740,000</t>
+          <t>1,820,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>15,050,000</t>
+          <t>10,020,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>6,810,000</t>
+          <t>4,530,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>5,110,000</t>
+          <t>3,410,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>10,070,000</t>
+          <t>6,700,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>11,663,000</t>
+          <t>6,816,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>10,490,000</t>
+          <t>6,980,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,082,000</t>
+          <t>712,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>8,261,527,816</t>
+          <t>8,453,088,178</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,862,471,602</t>
+          <t>2,265,434,802</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>-929,694,329</t>
+          <t>539,502,897</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
